--- a/data/trans_dic/BARTHEL_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,2; 94,22</t>
+          <t>5,89; 17,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,72; 95,32</t>
+          <t>4,57; 14,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,91; 90,68</t>
+          <t>9,61; 20,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,75; 90,32</t>
+          <t>9,51; 18,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,38; 93,55</t>
+          <t>6,15; 17,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,05; 81,65</t>
+          <t>18,5; 31,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,3; 82,51</t>
+          <t>17,13; 31,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,94; 78,5</t>
+          <t>21,51; 29,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,15; 92,93</t>
+          <t>7,44; 15,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77,9; 86,97</t>
+          <t>13,71; 22,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,51; 84,87</t>
+          <t>15,4; 24,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,78; 82,74</t>
+          <t>17,27; 23,53</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,33; 95,48</t>
+          <t>4,43; 13,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,51; 85,89</t>
+          <t>14,77; 28,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,54; 91,77</t>
+          <t>8,49; 18,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,76; 88,71</t>
+          <t>11,49; 20,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,03; 90,15</t>
+          <t>10,03; 21,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,67; 74,07</t>
+          <t>25,67; 39,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,02; 86,78</t>
+          <t>13,49; 25,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 80,04</t>
+          <t>20,05; 28,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,68; 91,55</t>
+          <t>8,44; 15,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,15; 77,33</t>
+          <t>22,82; 32,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79,78; 88,0</t>
+          <t>12,44; 20,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,49; 82,39</t>
+          <t>17,66; 23,61</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,53; 99,11</t>
+          <t>0,93; 8,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,26; 92,59</t>
+          <t>7,25; 23,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,09; 93,75</t>
+          <t>5,57; 17,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,36; 92,79</t>
+          <t>6,88; 16,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,92; 93,26</t>
+          <t>6,84; 17,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,13; 78,28</t>
+          <t>21,14; 37,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,93; 81,71</t>
+          <t>18,72; 34,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,09; 97,54</t>
+          <t>2,28; 22,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,87; 94,88</t>
+          <t>5,3; 12,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70,83; 82,69</t>
+          <t>17,18; 28,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,43; 86,07</t>
+          <t>14,51; 25,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,51; 96,72</t>
+          <t>2,99; 17,21</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,86; 95,26</t>
+          <t>5,26; 14,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,54; 90,63</t>
+          <t>9,61; 21,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,69; 94,36</t>
+          <t>5,62; 14,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,13; 91,32</t>
+          <t>8,62; 15,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,16; 89,21</t>
+          <t>11,07; 20,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,69; 84,94</t>
+          <t>14,59; 25,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,68; 84,48</t>
+          <t>15,65; 27,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74,76; 82,08</t>
+          <t>18,3; 25,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,83; 90,7</t>
+          <t>9,67; 16,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,79; 85,99</t>
+          <t>14,01; 22,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,67; 87,54</t>
+          <t>12,46; 20,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,99; 85,48</t>
+          <t>14,8; 20,01</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,41; 94,05</t>
+          <t>5,81; 10,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,53; 88,33</t>
+          <t>11,66; 18,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,51</t>
+          <t>9,5; 14,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,75; 88,9</t>
+          <t>11,08; 15,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,03</t>
+          <t>10,84; 16,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,66; 77,45</t>
+          <t>23,04; 29,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,82; 81,4</t>
+          <t>18,75; 25,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,29; 89,44</t>
+          <t>9,77; 23,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,81; 90,5</t>
+          <t>9,31; 13,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,52; 81,09</t>
+          <t>18,96; 23,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,02; 84,51</t>
+          <t>15,37; 19,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,97; 88,5</t>
+          <t>10,28; 19,11</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1509,62 +1509,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>28</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>58</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>102778</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>127217</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116802</t>
+          <t>19932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126813</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>133448</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>125246</t>
+          <t>41541</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>133052</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236225</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252463</t>
+          <t>53871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249854</t>
+          <t>60271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>259346</t>
+          <t>65329</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95669; 108340</t>
+          <t>6770; 19621</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119616; 133018</t>
+          <t>6380; 20355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107892; 123984</t>
+          <t>13146; 28543</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120027; 132613</t>
+          <t>13970; 27506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>124686; 139886</t>
+          <t>9204; 25677</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>113503; 136188</t>
+          <t>30851; 52946</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>118423; 143064</t>
+          <t>29706; 55182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124387; 139604</t>
+          <t>38247; 52621</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225244; 245812</t>
+          <t>19669; 40265</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>238623; 266411</t>
+          <t>42007; 69160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234169; 263212</t>
+          <t>47750; 75517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>249273; 268631</t>
+          <t>56064; 76396</t>
         </is>
       </c>
     </row>
@@ -1717,62 +1717,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>134157</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>122456</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143877</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>155442</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>129206</t>
+          <t>62214</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>178618</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>51733</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289598</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251662</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322495</t>
+          <t>61609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>300256</t>
+          <t>76805</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125943; 139296</t>
+          <t>6458; 20416</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110758; 133019</t>
+          <t>22869; 44447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134487; 151359</t>
+          <t>14006; 30362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127709; 142038</t>
+          <t>18391; 33275</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>144370; 164688</t>
+          <t>18331; 39698</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116125; 141787</t>
+          <t>49129; 76370</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>164412; 190184</t>
+          <t>29575; 56021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155860; 173634</t>
+          <t>43507; 61291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>278248; 300801</t>
+          <t>27724; 52550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232530; 267780</t>
+          <t>79016; 112559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>306434; 338005</t>
+          <t>47767; 79355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>288400; 310670</t>
+          <t>66593; 89033</t>
         </is>
       </c>
     </row>
@@ -1925,62 +1925,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>47</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>42</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>100659</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88430</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102599</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121290</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>119954</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100896</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>106064</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>327445</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>220613</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189326</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208663</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>448735</t>
+          <t>47880</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95534; 103443</t>
+          <t>968; 8479</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76931; 95924</t>
+          <t>7506; 24471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94432; 107841</t>
+          <t>6409; 20096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114156; 127075</t>
+          <t>9426; 22465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>111292; 126694</t>
+          <t>9294; 24062</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87619; 110383</t>
+          <t>29807; 52248</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94008; 116512</t>
+          <t>26687; 49167</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>280874; 350805</t>
+          <t>8199; 80951</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211089; 227932</t>
+          <t>12730; 29720</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>173273; 202274</t>
+          <t>42025; 70381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194322; 221736</t>
+          <t>37390; 64590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>409755; 480316</t>
+          <t>14848; 85488</t>
         </is>
       </c>
     </row>
@@ -2133,62 +2133,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>150</t>
         </is>
       </c>
     </row>
@@ -2201,62 +2201,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>124972</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>137998</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157952</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180063</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>176904</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>195178</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>191448</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>214568</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>301876</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333176</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349401</t>
+          <t>67999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>394632</t>
+          <t>83146</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>117811; 130707</t>
+          <t>7223; 19911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126927; 146468</t>
+          <t>15526; 35056</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149636; 164770</t>
+          <t>9820; 25946</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171985; 186682</t>
+          <t>17632; 32398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165271; 186253</t>
+          <t>23115; 43255</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>182057; 207038</t>
+          <t>35553; 61982</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>176452; 205091</t>
+          <t>38006; 66616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>204359; 224373</t>
+          <t>50013; 68940</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>286576; 313808</t>
+          <t>33451; 57891</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>315337; 348589</t>
+          <t>56811; 90109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>332534; 365386</t>
+          <t>52006; 84451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>382159; 408422</t>
+          <t>70728; 95604</t>
         </is>
       </c>
     </row>
@@ -2341,62 +2341,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>386</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>526</t>
         </is>
       </c>
     </row>
@@ -2409,62 +2409,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>462565</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>476102</t>
+          <t>83535</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521230</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>563210</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>585747</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>550525</t>
+          <t>192450</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>609182</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>839761</t>
+          <t>188049</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1048312</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1026627</t>
+          <t>275985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1130412</t>
+          <t>238847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1402970</t>
+          <t>273160</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>449238; 472568</t>
+          <t>29182; 52301</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>456251; 494339</t>
+          <t>65275; 101241</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>506213; 535239</t>
+          <t>56165; 86052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>549445; 576379</t>
+          <t>71839; 99136</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>565581; 602613</t>
+          <t>73382; 109071</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>524999; 575445</t>
+          <t>171211; 219312</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>582046; 633231</t>
+          <t>145837; 198271</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>784166; 919250</t>
+          <t>100373; 241687</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1023807; 1067262</t>
+          <t>109799; 153994</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>996815; 1056237</t>
+          <t>246971; 309586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1095662; 1157194</t>
+          <t>210422; 267800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1357089; 1483384</t>
+          <t>172260; 320343</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/BARTHEL_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 17,06</t>
+          <t>6,33; 17,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 14,59</t>
+          <t>4,94; 14,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 20,87</t>
+          <t>9,51; 21,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,73</t>
+          <t>9,1; 17,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 17,17</t>
+          <t>6,22; 17,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 31,74</t>
+          <t>18,75; 31,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 31,83</t>
+          <t>16,82; 30,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,51; 29,59</t>
+          <t>21,7; 29,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 15,22</t>
+          <t>7,51; 15,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 22,58</t>
+          <t>13,6; 22,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,4; 24,35</t>
+          <t>15,17; 24,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 23,53</t>
+          <t>16,57; 22,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,99</t>
+          <t>4,07; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 28,7</t>
+          <t>14,27; 28,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 18,41</t>
+          <t>8,38; 17,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 20,78</t>
+          <t>11,36; 20,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 21,73</t>
+          <t>9,64; 21,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,67; 39,9</t>
+          <t>25,9; 39,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 25,56</t>
+          <t>13,21; 24,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 28,25</t>
+          <t>19,5; 27,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,99</t>
+          <t>8,63; 16,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,82; 32,5</t>
+          <t>22,73; 32,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 20,66</t>
+          <t>12,35; 19,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 23,61</t>
+          <t>17,31; 23,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,12</t>
+          <t>0,88; 8,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 23,62</t>
+          <t>7,54; 24,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 17,47</t>
+          <t>6,18; 18,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,4</t>
+          <t>6,77; 16,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 17,71</t>
+          <t>6,7; 18,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 37,05</t>
+          <t>20,53; 36,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 34,48</t>
+          <t>17,8; 33,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 22,51</t>
+          <t>16,43; 26,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,37</t>
+          <t>5,09; 12,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 28,77</t>
+          <t>17,55; 28,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,07</t>
+          <t>14,43; 24,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,21</t>
+          <t>12,99; 19,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 14,51</t>
+          <t>4,86; 14,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 21,69</t>
+          <t>9,17; 21,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 14,86</t>
+          <t>6,07; 14,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,85</t>
+          <t>8,72; 15,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 20,72</t>
+          <t>10,55; 20,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 25,43</t>
+          <t>15,35; 25,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 27,44</t>
+          <t>15,26; 27,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 25,22</t>
+          <t>18,93; 26,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 16,73</t>
+          <t>9,45; 16,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 22,23</t>
+          <t>14,19; 22,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,23</t>
+          <t>12,5; 20,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,01</t>
+          <t>15,24; 20,6</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,41</t>
+          <t>6,2; 10,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,09</t>
+          <t>11,98; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,29</t>
+          <t>10,62; 14,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,11</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,52</t>
+          <t>22,45; 28,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,49</t>
+          <t>18,76; 25,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 23,51</t>
+          <t>20,85; 25,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,06</t>
+          <t>9,36; 12,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,77</t>
+          <t>18,97; 23,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,37; 19,56</t>
+          <t>15,45; 19,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,11</t>
+          <t>16,9; 20,01</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45313</t>
+          <t>48188</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>68656</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6770; 19621</t>
+          <t>7277; 19701</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6380; 20355</t>
+          <t>6890; 20286</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13146; 28543</t>
+          <t>13005; 29047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13970; 27506</t>
+          <t>14720; 27834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9204; 25677</t>
+          <t>9303; 25902</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30851; 52946</t>
+          <t>31277; 52633</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29706; 55182</t>
+          <t>29164; 52019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38247; 52621</t>
+          <t>41122; 56436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19669; 40265</t>
+          <t>19876; 40580</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42007; 69160</t>
+          <t>41661; 70406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47750; 75517</t>
+          <t>47042; 75808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56064; 76396</t>
+          <t>58209; 80743</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76805</t>
+          <t>83850</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6458; 20416</t>
+          <t>5945; 18017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22869; 44447</t>
+          <t>22106; 44752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14006; 30362</t>
+          <t>13827; 29376</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18391; 33275</t>
+          <t>20245; 36873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18331; 39698</t>
+          <t>17612; 39083</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49129; 76370</t>
+          <t>49577; 75356</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29575; 56021</t>
+          <t>28945; 54124</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43507; 61291</t>
+          <t>46872; 66428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27724; 52550</t>
+          <t>28350; 53092</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79016; 112559</t>
+          <t>78716; 111532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47767; 79355</t>
+          <t>47441; 76335</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66593; 89033</t>
+          <t>72436; 97152</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>53760</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>968; 8479</t>
+          <t>921; 8733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7506; 24471</t>
+          <t>7806; 25355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6409; 20096</t>
+          <t>7113; 20895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9426; 22465</t>
+          <t>10814; 25608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9294; 24062</t>
+          <t>9103; 25273</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29807; 52248</t>
+          <t>28947; 50847</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26687; 49167</t>
+          <t>25382; 47984</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8199; 80951</t>
+          <t>28629; 46112</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12730; 29720</t>
+          <t>12226; 29386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42025; 70381</t>
+          <t>42921; 69953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37390; 64590</t>
+          <t>37172; 64320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14848; 85488</t>
+          <t>43411; 66413</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83146</t>
+          <t>90681</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7223; 19911</t>
+          <t>6664; 19303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15526; 35056</t>
+          <t>14815; 35263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9820; 25946</t>
+          <t>10607; 25895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17632; 32398</t>
+          <t>18693; 33249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23115; 43255</t>
+          <t>22031; 43066</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35553; 61982</t>
+          <t>37424; 62128</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38006; 66616</t>
+          <t>37053; 65624</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50013; 68940</t>
+          <t>55467; 77365</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33451; 57891</t>
+          <t>32689; 57720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56811; 90109</t>
+          <t>57536; 89216</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52006; 84451</t>
+          <t>52191; 84620</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70728; 95604</t>
+          <t>77334; 104530</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29182; 52301</t>
+          <t>31162; 53936</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65275; 101241</t>
+          <t>67035; 102984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56165; 86052</t>
+          <t>56185; 86038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71839; 99136</t>
+          <t>75881; 105557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>73382; 109071</t>
+          <t>75498; 111199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>171211; 219312</t>
+          <t>166780; 215353</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>145837; 198271</t>
+          <t>145972; 195591</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100373; 241687</t>
+          <t>187084; 226763</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>109799; 153994</t>
+          <t>110431; 153159</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246971; 309586</t>
+          <t>247130; 306910</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210422; 267800</t>
+          <t>211551; 270154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>172260; 320343</t>
+          <t>272374; 322447</t>
         </is>
       </c>
     </row>
